--- a/AAII_Financials/Quarterly/ADMG_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ADMG_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
   <si>
     <t>ADMG</t>
   </si>
@@ -656,110 +656,114 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:X102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44834</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44742</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44651</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44561</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44377</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43555</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43373</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43281</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>43190</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43008</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42916</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42825</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42735</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>42643</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -809,25 +813,28 @@
         <v>0</v>
       </c>
       <c r="S8" s="3">
+        <v>0</v>
+      </c>
+      <c r="T8" s="3">
         <v>600</v>
       </c>
-      <c r="T8" s="3">
-        <v>0</v>
-      </c>
       <c r="U8" s="3">
         <v>0</v>
       </c>
       <c r="V8" s="3">
+        <v>0</v>
+      </c>
+      <c r="W8" s="3">
         <v>600</v>
       </c>
-      <c r="W8" s="3">
-        <v>0</v>
-      </c>
       <c r="X8" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y8" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
@@ -858,14 +865,14 @@
       <c r="L9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M9" s="3">
-        <v>0</v>
+      <c r="M9" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N9" s="3">
         <v>0</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>4</v>
+      <c r="O9" s="3">
+        <v>0</v>
       </c>
       <c r="P9" s="3" t="s">
         <v>4</v>
@@ -876,26 +883,29 @@
       <c r="R9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S9" s="3">
+      <c r="S9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T9" s="3">
         <v>600</v>
       </c>
-      <c r="T9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="U9" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V9" s="3">
+      <c r="V9" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W9" s="3">
         <v>300</v>
       </c>
-      <c r="W9" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X9" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y9" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -926,14 +936,14 @@
       <c r="L10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M10" s="3">
-        <v>0</v>
+      <c r="M10" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N10" s="3">
         <v>0</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>4</v>
+      <c r="O10" s="3">
+        <v>0</v>
       </c>
       <c r="P10" s="3" t="s">
         <v>4</v>
@@ -944,26 +954,29 @@
       <c r="R10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="S10" s="3">
-        <v>0</v>
-      </c>
-      <c r="T10" s="3" t="s">
-        <v>4</v>
+      <c r="S10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="T10" s="3">
+        <v>0</v>
       </c>
       <c r="U10" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V10" s="3">
+      <c r="V10" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="W10" s="3">
         <v>300</v>
       </c>
-      <c r="W10" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="X10" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y10" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -988,8 +1001,9 @@
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
       <c r="X11" s="3"/>
-    </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -1056,8 +1070,11 @@
       <c r="X12" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y12" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1124,8 +1141,11 @@
       <c r="X13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1159,11 +1179,11 @@
       <c r="M14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
-      <c r="O14" s="3" t="s">
-        <v>4</v>
+      <c r="N14" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
+        <v>0</v>
       </c>
       <c r="P14" s="3" t="s">
         <v>4</v>
@@ -1177,8 +1197,8 @@
       <c r="S14" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
@@ -1192,8 +1212,11 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1260,8 +1283,11 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.2">
+      <c r="Y15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1283,8 +1309,9 @@
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
       <c r="X16" s="3"/>
-    </row>
-    <row r="17" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1316,43 +1343,46 @@
         <v>0</v>
       </c>
       <c r="M17" s="3">
+        <v>0</v>
+      </c>
+      <c r="N17" s="3">
         <v>100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>-2300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>900</v>
       </c>
     </row>
-    <row r="18" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1384,43 +1414,46 @@
         <v>0</v>
       </c>
       <c r="M18" s="3">
+        <v>0</v>
+      </c>
+      <c r="N18" s="3">
         <v>-100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-200</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-1000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-2000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-1000</v>
-      </c>
-      <c r="V18" s="3">
-        <v>-1100</v>
       </c>
       <c r="W18" s="3">
         <v>-1100</v>
       </c>
       <c r="X18" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="Y18" s="3">
         <v>-900</v>
       </c>
     </row>
-    <row r="19" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1445,8 +1478,9 @@
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
       <c r="X19" s="3"/>
-    </row>
-    <row r="20" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1481,40 +1515,43 @@
         <v>0</v>
       </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>2200</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
         <v>0</v>
       </c>
       <c r="Q20" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="R20" s="3">
         <v>300</v>
       </c>
       <c r="S20" s="3">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1000</v>
       </c>
-      <c r="W20" s="3">
-        <v>0</v>
-      </c>
       <c r="X20" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y20" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1524,8 +1561,8 @@
       <c r="E21" s="3">
         <v>0</v>
       </c>
-      <c r="F21" s="3" t="s">
-        <v>4</v>
+      <c r="F21" s="3">
+        <v>0</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>4</v>
@@ -1545,44 +1582,47 @@
       <c r="L21" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M21" s="3">
+      <c r="M21" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="N21" s="3">
         <v>-100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5200</v>
-      </c>
-      <c r="O21" s="3">
-        <v>-300</v>
       </c>
       <c r="P21" s="3">
         <v>-300</v>
       </c>
       <c r="Q21" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R21" s="3">
         <v>900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>2600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-1500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-200</v>
       </c>
     </row>
-    <row r="22" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1592,11 +1632,11 @@
       <c r="E22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>4</v>
+      <c r="F22" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="G22" s="3">
+        <v>0</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>4</v>
@@ -1619,8 +1659,8 @@
       <c r="N22" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="O22" s="3">
-        <v>300</v>
+      <c r="O22" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="P22" s="3">
         <v>300</v>
@@ -1635,10 +1675,10 @@
         <v>300</v>
       </c>
       <c r="T22" s="3">
+        <v>300</v>
+      </c>
+      <c r="U22" s="3">
         <v>500</v>
-      </c>
-      <c r="U22" s="3">
-        <v>300</v>
       </c>
       <c r="V22" s="3">
         <v>300</v>
@@ -1649,8 +1689,11 @@
       <c r="X22" s="3">
         <v>300</v>
       </c>
-    </row>
-    <row r="23" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y22" s="3">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1682,54 +1725,57 @@
         <v>0</v>
       </c>
       <c r="M23" s="3">
+        <v>0</v>
+      </c>
+      <c r="N23" s="3">
         <v>-100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>4500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-1300</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-1200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-1300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-2800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-1300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-2400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-1300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="24" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="D24" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="3">
+        <v>0</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G24" s="3">
         <v>0</v>
@@ -1785,8 +1831,11 @@
       <c r="X24" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y24" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1853,8 +1902,11 @@
       <c r="X25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1886,43 +1938,46 @@
         <v>0</v>
       </c>
       <c r="M26" s="3">
+        <v>0</v>
+      </c>
+      <c r="N26" s="3">
         <v>-100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>4500</v>
-      </c>
-      <c r="O26" s="3">
-        <v>-1200</v>
       </c>
       <c r="P26" s="3">
         <v>-1200</v>
       </c>
       <c r="Q26" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R26" s="3">
         <v>-200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-1300</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-2800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-1300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-2400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-1300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="27" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1954,43 +2009,46 @@
         <v>0</v>
       </c>
       <c r="M27" s="3">
+        <v>0</v>
+      </c>
+      <c r="N27" s="3">
         <v>-100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4500</v>
-      </c>
-      <c r="O27" s="3">
-        <v>-1200</v>
       </c>
       <c r="P27" s="3">
         <v>-1200</v>
       </c>
       <c r="Q27" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R27" s="3">
         <v>-200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-1300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-2800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-1300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-2400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-1300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="28" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2057,8 +2115,11 @@
       <c r="X28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2089,29 +2150,29 @@
       <c r="L29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>20600</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="P29" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="Q29" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="R29" s="3">
         <v>-1300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="S29" s="3">
         <v>-6600</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
+      <c r="T29" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="U29" s="3">
         <v>0</v>
@@ -2125,8 +2186,11 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2193,8 +2257,11 @@
       <c r="X30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2261,8 +2328,11 @@
       <c r="X31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2297,40 +2367,43 @@
         <v>0</v>
       </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-2200</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
         <v>0</v>
       </c>
       <c r="Q32" s="3">
-        <v>-300</v>
+        <v>0</v>
       </c>
       <c r="R32" s="3">
         <v>-300</v>
       </c>
       <c r="S32" s="3">
-        <v>0</v>
+        <v>-300</v>
       </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1000</v>
       </c>
-      <c r="W32" s="3">
-        <v>0</v>
-      </c>
       <c r="X32" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y32" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2362,43 +2435,46 @@
         <v>0</v>
       </c>
       <c r="M33" s="3">
+        <v>0</v>
+      </c>
+      <c r="N33" s="3">
         <v>-100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>25100</v>
-      </c>
-      <c r="O33" s="3">
-        <v>-1200</v>
       </c>
       <c r="P33" s="3">
         <v>-1200</v>
       </c>
       <c r="Q33" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R33" s="3">
         <v>-1400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-7200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-1300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-2800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-1300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-2400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-1300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="34" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2465,8 +2541,11 @@
       <c r="X34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2498,116 +2577,122 @@
         <v>0</v>
       </c>
       <c r="M35" s="3">
+        <v>0</v>
+      </c>
+      <c r="N35" s="3">
         <v>-100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>25100</v>
-      </c>
-      <c r="O35" s="3">
-        <v>-1200</v>
       </c>
       <c r="P35" s="3">
         <v>-1200</v>
       </c>
       <c r="Q35" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R35" s="3">
         <v>-1400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-7200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-1300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-2800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-1300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-2400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-1300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="37" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44834</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44742</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44651</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44561</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44377</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43555</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43373</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43281</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>43190</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43008</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42916</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42825</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42735</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>42643</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="39" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2632,8 +2717,9 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
       <c r="X39" s="3"/>
-    </row>
-    <row r="40" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2658,8 +2744,9 @@
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
       <c r="X40" s="3"/>
-    </row>
-    <row r="41" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
@@ -2709,16 +2796,16 @@
         <v>0</v>
       </c>
       <c r="S41" s="3">
+        <v>0</v>
+      </c>
+      <c r="T41" s="3">
         <v>100</v>
       </c>
-      <c r="T41" s="3">
-        <v>0</v>
-      </c>
       <c r="U41" s="3">
         <v>0</v>
       </c>
       <c r="V41" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="W41" s="3">
         <v>100</v>
@@ -2726,8 +2813,11 @@
       <c r="X41" s="3">
         <v>100</v>
       </c>
-    </row>
-    <row r="42" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y41" s="3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2794,8 +2884,11 @@
       <c r="X42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2820,35 +2913,35 @@
       <c r="J43" s="3">
         <v>0</v>
       </c>
-      <c r="K43" s="3" t="s">
-        <v>4</v>
+      <c r="K43" s="3">
+        <v>0</v>
       </c>
       <c r="L43" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M43" s="3">
-        <v>0</v>
+      <c r="M43" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N43" s="3">
+        <v>0</v>
+      </c>
+      <c r="O43" s="3">
         <v>100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2900</v>
-      </c>
-      <c r="R43" s="3">
-        <v>2800</v>
       </c>
       <c r="S43" s="3">
         <v>2800</v>
       </c>
       <c r="T43" s="3">
-        <v>2700</v>
+        <v>2800</v>
       </c>
       <c r="U43" s="3">
         <v>2700</v>
@@ -2857,13 +2950,16 @@
         <v>2700</v>
       </c>
       <c r="W43" s="3">
+        <v>2700</v>
+      </c>
+      <c r="X43" s="3">
         <v>2900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2800</v>
       </c>
     </row>
-    <row r="44" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2901,10 +2997,10 @@
         <v>0</v>
       </c>
       <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
         <v>400</v>
-      </c>
-      <c r="P44" s="3">
-        <v>500</v>
       </c>
       <c r="Q44" s="3">
         <v>500</v>
@@ -2913,7 +3009,7 @@
         <v>500</v>
       </c>
       <c r="S44" s="3">
-        <v>700</v>
+        <v>500</v>
       </c>
       <c r="T44" s="3">
         <v>700</v>
@@ -2925,18 +3021,21 @@
         <v>700</v>
       </c>
       <c r="W44" s="3">
-        <v>1400</v>
+        <v>700</v>
       </c>
       <c r="X44" s="3">
         <v>1400</v>
       </c>
-    </row>
-    <row r="45" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y44" s="3">
+        <v>1400</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
@@ -2944,11 +3043,11 @@
       <c r="F45" s="3">
         <v>0</v>
       </c>
-      <c r="G45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="H45" s="3">
-        <v>0</v>
+      <c r="G45" s="3">
+        <v>0</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="I45" s="3">
         <v>0</v>
@@ -2962,49 +3061,52 @@
       <c r="L45" s="3">
         <v>0</v>
       </c>
-      <c r="M45" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="N45" s="3">
-        <v>0</v>
+      <c r="M45" s="3">
+        <v>0</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
         <v>3900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>4200</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>4500</v>
       </c>
       <c r="R45" s="3">
         <v>4500</v>
       </c>
       <c r="S45" s="3">
+        <v>4500</v>
+      </c>
+      <c r="T45" s="3">
         <v>1100</v>
-      </c>
-      <c r="T45" s="3">
-        <v>900</v>
       </c>
       <c r="U45" s="3">
         <v>900</v>
       </c>
       <c r="V45" s="3">
+        <v>900</v>
+      </c>
+      <c r="W45" s="3">
         <v>100</v>
       </c>
-      <c r="W45" s="3">
-        <v>0</v>
-      </c>
       <c r="X45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E46" s="3">
         <v>0</v>
@@ -3034,40 +3136,43 @@
         <v>0</v>
       </c>
       <c r="N46" s="3">
+        <v>0</v>
+      </c>
+      <c r="O46" s="3">
         <v>100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>7000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>7400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>7900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>7800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3500</v>
-      </c>
-      <c r="W46" s="3">
-        <v>4400</v>
       </c>
       <c r="X46" s="3">
         <v>4400</v>
       </c>
-    </row>
-    <row r="47" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y46" s="3">
+        <v>4400</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3134,8 +3239,11 @@
       <c r="X47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
@@ -3160,50 +3268,53 @@
       <c r="J48" s="3">
         <v>0</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>4</v>
+      <c r="K48" s="3">
+        <v>0</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M48" s="3">
-        <v>400</v>
+      <c r="M48" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N48" s="3">
         <v>400</v>
       </c>
       <c r="O48" s="3">
+        <v>400</v>
+      </c>
+      <c r="P48" s="3">
         <v>20100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>21600</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>23300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>23100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>29600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>29800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>30100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>30600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>32400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>33300</v>
       </c>
     </row>
-    <row r="49" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -3241,37 +3352,40 @@
         <v>0</v>
       </c>
       <c r="O49" s="3">
+        <v>0</v>
+      </c>
+      <c r="P49" s="3">
         <v>8700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>9100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>9600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>9200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>9100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>8900</v>
-      </c>
-      <c r="U49" s="3">
-        <v>8800</v>
       </c>
       <c r="V49" s="3">
         <v>8800</v>
       </c>
       <c r="W49" s="3">
+        <v>8800</v>
+      </c>
+      <c r="X49" s="3">
         <v>9100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>9200</v>
       </c>
     </row>
-    <row r="50" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3338,8 +3452,11 @@
       <c r="X50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3406,8 +3523,11 @@
       <c r="X51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3445,37 +3565,40 @@
         <v>0</v>
       </c>
       <c r="O52" s="3">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="P52" s="3">
         <v>400</v>
       </c>
       <c r="Q52" s="3">
+        <v>400</v>
+      </c>
+      <c r="R52" s="3">
         <v>500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>400</v>
       </c>
-      <c r="S52" s="3" t="s">
-        <v>4</v>
-      </c>
       <c r="T52" s="3" t="s">
         <v>4</v>
       </c>
       <c r="U52" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="V52" s="3">
-        <v>0</v>
+      <c r="V52" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="W52" s="3">
         <v>0</v>
       </c>
-      <c r="X52" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X52" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3542,13 +3665,16 @@
       <c r="X53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E54" s="3">
         <v>0</v>
@@ -3575,43 +3701,46 @@
         <v>0</v>
       </c>
       <c r="M54" s="3">
+        <v>0</v>
+      </c>
+      <c r="N54" s="3">
         <v>400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>36200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>38500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>41200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>40600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>43500</v>
-      </c>
-      <c r="T54" s="3">
-        <v>43100</v>
       </c>
       <c r="U54" s="3">
         <v>43100</v>
       </c>
       <c r="V54" s="3">
+        <v>43100</v>
+      </c>
+      <c r="W54" s="3">
         <v>42900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>46000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>46900</v>
       </c>
     </row>
-    <row r="55" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3636,8 +3765,9 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
       <c r="X55" s="3"/>
-    </row>
-    <row r="56" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3662,8 +3792,9 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
       <c r="X56" s="3"/>
-    </row>
-    <row r="57" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3695,43 +3826,46 @@
         <v>0</v>
       </c>
       <c r="M57" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N57" s="3">
         <v>100</v>
       </c>
       <c r="O57" s="3">
+        <v>100</v>
+      </c>
+      <c r="P57" s="3">
         <v>15400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>15700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>15300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>15400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>14900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>14300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>14100</v>
-      </c>
-      <c r="W57" s="3">
-        <v>16300</v>
       </c>
       <c r="X57" s="3">
         <v>16300</v>
       </c>
-    </row>
-    <row r="58" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y57" s="3">
+        <v>16300</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -3750,8 +3884,8 @@
       <c r="H58" s="3">
         <v>0</v>
       </c>
-      <c r="I58" s="3" t="s">
-        <v>4</v>
+      <c r="I58" s="3">
+        <v>0</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>4</v>
@@ -3762,55 +3896,58 @@
       <c r="L58" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
+      <c r="M58" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N58" s="3">
         <v>0</v>
       </c>
       <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
         <v>43700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>45300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>47500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>45500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>42800</v>
-      </c>
-      <c r="T58" s="3">
-        <v>200</v>
       </c>
       <c r="U58" s="3">
         <v>200</v>
       </c>
       <c r="V58" s="3">
+        <v>200</v>
+      </c>
+      <c r="W58" s="3">
         <v>300</v>
-      </c>
-      <c r="W58" s="3">
-        <v>200</v>
       </c>
       <c r="X58" s="3">
         <v>200</v>
       </c>
-    </row>
-    <row r="59" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y58" s="3">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
         <v>0</v>
       </c>
-      <c r="E59" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F59" s="3">
-        <v>0</v>
+      <c r="E59" s="3">
+        <v>0</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="G59" s="3">
         <v>0</v>
@@ -3837,37 +3974,40 @@
         <v>0</v>
       </c>
       <c r="O59" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="P59" s="3">
         <v>1000</v>
       </c>
       <c r="Q59" s="3">
-        <v>1100</v>
+        <v>1000</v>
       </c>
       <c r="R59" s="3">
         <v>1100</v>
       </c>
       <c r="S59" s="3">
+        <v>1100</v>
+      </c>
+      <c r="T59" s="3">
         <v>1500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>42600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>41600</v>
-      </c>
-      <c r="V59" s="3">
-        <v>41100</v>
       </c>
       <c r="W59" s="3">
         <v>41100</v>
       </c>
       <c r="X59" s="3">
+        <v>41100</v>
+      </c>
+      <c r="Y59" s="3">
         <v>40800</v>
       </c>
     </row>
-    <row r="60" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3890,52 +4030,55 @@
         <v>0</v>
       </c>
       <c r="J60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K60" s="3">
         <v>100</v>
       </c>
       <c r="L60" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M60" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N60" s="3">
         <v>100</v>
       </c>
       <c r="O60" s="3">
+        <v>100</v>
+      </c>
+      <c r="P60" s="3">
         <v>60100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>62000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>64800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>61800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>59700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>57700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>56100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>55500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>57600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="61" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
@@ -3973,7 +4116,7 @@
         <v>0</v>
       </c>
       <c r="O61" s="3">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="P61" s="3">
         <v>200</v>
@@ -3985,7 +4128,7 @@
         <v>200</v>
       </c>
       <c r="S61" s="3">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="T61" s="3">
         <v>0</v>
@@ -4002,8 +4145,11 @@
       <c r="X61" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="62" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y61" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
@@ -4070,8 +4216,11 @@
       <c r="X62" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="63" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y62" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4138,8 +4287,11 @@
       <c r="X63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4206,8 +4358,11 @@
       <c r="X64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4274,8 +4429,11 @@
       <c r="X65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
@@ -4298,52 +4456,55 @@
         <v>0</v>
       </c>
       <c r="J66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K66" s="3">
         <v>100</v>
       </c>
       <c r="L66" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M66" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="N66" s="3">
         <v>100</v>
       </c>
       <c r="O66" s="3">
+        <v>100</v>
+      </c>
+      <c r="P66" s="3">
         <v>60300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>62200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>65000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>62000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>59700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>57700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>56100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>55500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>57600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>57300</v>
       </c>
     </row>
-    <row r="67" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4368,8 +4529,9 @@
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
       <c r="X67" s="3"/>
-    </row>
-    <row r="68" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4436,8 +4598,11 @@
       <c r="X68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4504,8 +4669,11 @@
       <c r="X69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4572,8 +4740,11 @@
       <c r="X70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4640,8 +4811,11 @@
       <c r="X71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
@@ -4655,7 +4829,7 @@
         <v>-9600</v>
       </c>
       <c r="G72" s="3">
-        <v>-9500</v>
+        <v>-9600</v>
       </c>
       <c r="H72" s="3">
         <v>-9500</v>
@@ -4670,46 +4844,49 @@
         <v>-9500</v>
       </c>
       <c r="L72" s="3">
+        <v>-9500</v>
+      </c>
+      <c r="M72" s="3">
         <v>-9400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-9100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-9000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-34100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-32900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-31700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-30300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-25400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-24100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-22700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-21400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-20000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-18600</v>
       </c>
     </row>
-    <row r="73" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4776,8 +4953,11 @@
       <c r="X73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4844,8 +5024,11 @@
       <c r="X74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4912,8 +5095,11 @@
       <c r="X75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
@@ -4936,52 +5122,55 @@
         <v>0</v>
       </c>
       <c r="J76" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="K76" s="3">
         <v>-100</v>
       </c>
       <c r="L76" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="M76" s="3">
+        <v>0</v>
+      </c>
+      <c r="N76" s="3">
         <v>300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-24100</v>
-      </c>
-      <c r="P76" s="3">
-        <v>-23700</v>
       </c>
       <c r="Q76" s="3">
         <v>-23700</v>
       </c>
       <c r="R76" s="3">
+        <v>-23700</v>
+      </c>
+      <c r="S76" s="3">
         <v>-21500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-16200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-14600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-13000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-12600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-11600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-10400</v>
       </c>
     </row>
-    <row r="77" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5048,81 +5237,87 @@
       <c r="X77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:24" x14ac:dyDescent="0.2">
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:24" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44834</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44742</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44651</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44561</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44377</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43555</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43373</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43281</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>43190</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43008</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42916</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42825</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42735</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>42643</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>42551</v>
       </c>
     </row>
-    <row r="81" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -5154,43 +5349,46 @@
         <v>0</v>
       </c>
       <c r="M81" s="3">
+        <v>0</v>
+      </c>
+      <c r="N81" s="3">
         <v>-100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>25100</v>
-      </c>
-      <c r="O81" s="3">
-        <v>-1200</v>
       </c>
       <c r="P81" s="3">
         <v>-1200</v>
       </c>
       <c r="Q81" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="R81" s="3">
         <v>-1400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-7200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-1300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-2800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-1300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-2400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-1300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="82" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5215,8 +5413,9 @@
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
       <c r="X82" s="3"/>
-    </row>
-    <row r="83" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -5241,38 +5440,38 @@
       <c r="J83" s="3">
         <v>0</v>
       </c>
-      <c r="K83" s="3" t="s">
-        <v>4</v>
+      <c r="K83" s="3">
+        <v>0</v>
       </c>
       <c r="L83" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M83" s="3">
-        <v>0</v>
+      <c r="M83" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N83" s="3">
-        <v>700</v>
+        <v>0</v>
       </c>
       <c r="O83" s="3">
         <v>700</v>
       </c>
       <c r="P83" s="3">
+        <v>700</v>
+      </c>
+      <c r="Q83" s="3">
         <v>600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>2900</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>1400</v>
-      </c>
-      <c r="U83" s="3">
-        <v>700</v>
       </c>
       <c r="V83" s="3">
         <v>700</v>
@@ -5283,8 +5482,11 @@
       <c r="X83" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="84" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y83" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5351,8 +5553,11 @@
       <c r="X84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5419,8 +5624,11 @@
       <c r="X85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5487,8 +5695,11 @@
       <c r="X86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5555,8 +5766,11 @@
       <c r="X87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5623,8 +5837,11 @@
       <c r="X88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
@@ -5644,11 +5861,11 @@
         <v>0</v>
       </c>
       <c r="I89" s="3">
+        <v>0</v>
+      </c>
+      <c r="J89" s="3">
         <v>-100</v>
       </c>
-      <c r="J89" s="3">
-        <v>0</v>
-      </c>
       <c r="K89" s="3">
         <v>0</v>
       </c>
@@ -5662,37 +5879,40 @@
         <v>0</v>
       </c>
       <c r="O89" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="P89" s="3">
         <v>-100</v>
       </c>
       <c r="Q89" s="3">
+        <v>-100</v>
+      </c>
+      <c r="R89" s="3">
         <v>-300</v>
-      </c>
-      <c r="R89" s="3">
-        <v>-200</v>
       </c>
       <c r="S89" s="3">
         <v>-200</v>
       </c>
       <c r="T89" s="3">
+        <v>-200</v>
+      </c>
+      <c r="U89" s="3">
         <v>-500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>-300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>-600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>-400</v>
       </c>
     </row>
-    <row r="90" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5717,8 +5937,9 @@
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
       <c r="X90" s="3"/>
-    </row>
-    <row r="91" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -5761,11 +5982,11 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="R91" s="3">
-        <v>0</v>
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="S91" s="3">
         <v>0</v>
@@ -5777,16 +5998,19 @@
         <v>0</v>
       </c>
       <c r="V91" s="3">
+        <v>0</v>
+      </c>
+      <c r="W91" s="3">
         <v>-600</v>
       </c>
-      <c r="W91" s="3">
-        <v>0</v>
-      </c>
-      <c r="X91" s="3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="92" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="X91" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y91" s="3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5853,8 +6077,11 @@
       <c r="X92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5921,8 +6148,11 @@
       <c r="X93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
@@ -5947,14 +6177,14 @@
       <c r="J94" s="3">
         <v>0</v>
       </c>
-      <c r="K94" s="3" t="s">
-        <v>4</v>
+      <c r="K94" s="3">
+        <v>0</v>
       </c>
       <c r="L94" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M94" s="3">
-        <v>0</v>
+      <c r="M94" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N94" s="3">
         <v>0</v>
@@ -5981,16 +6211,19 @@
         <v>0</v>
       </c>
       <c r="V94" s="3">
+        <v>0</v>
+      </c>
+      <c r="W94" s="3">
         <v>-200</v>
       </c>
-      <c r="W94" s="3">
-        <v>0</v>
-      </c>
       <c r="X94" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-100</v>
       </c>
     </row>
-    <row r="95" spans="3:24" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6015,8 +6248,9 @@
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
       <c r="X95" s="3"/>
-    </row>
-    <row r="96" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -6083,8 +6317,11 @@
       <c r="X96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6151,8 +6388,11 @@
       <c r="X97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6219,8 +6459,11 @@
       <c r="X98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6287,8 +6530,11 @@
       <c r="X99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
@@ -6308,11 +6554,11 @@
         <v>0</v>
       </c>
       <c r="I100" s="3">
+        <v>0</v>
+      </c>
+      <c r="J100" s="3">
         <v>100</v>
       </c>
-      <c r="J100" s="3">
-        <v>0</v>
-      </c>
       <c r="K100" s="3">
         <v>0</v>
       </c>
@@ -6326,37 +6572,40 @@
         <v>0</v>
       </c>
       <c r="O100" s="3">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="P100" s="3">
         <v>100</v>
       </c>
       <c r="Q100" s="3">
+        <v>100</v>
+      </c>
+      <c r="R100" s="3">
         <v>300</v>
-      </c>
-      <c r="R100" s="3">
-        <v>200</v>
       </c>
       <c r="S100" s="3">
         <v>200</v>
       </c>
       <c r="T100" s="3">
+        <v>200</v>
+      </c>
+      <c r="U100" s="3">
         <v>400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>2200</v>
-      </c>
-      <c r="W100" s="3">
-        <v>600</v>
       </c>
       <c r="X100" s="3">
         <v>600</v>
       </c>
-    </row>
-    <row r="101" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y100" s="3">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -6381,14 +6630,14 @@
       <c r="J101" s="3">
         <v>0</v>
       </c>
-      <c r="K101" s="3" t="s">
-        <v>4</v>
+      <c r="K101" s="3">
+        <v>0</v>
       </c>
       <c r="L101" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -6423,8 +6672,11 @@
       <c r="X101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:24" x14ac:dyDescent="0.2">
+      <c r="Y101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
@@ -6471,24 +6723,27 @@
         <v>0</v>
       </c>
       <c r="R102" s="3">
+        <v>0</v>
+      </c>
+      <c r="S102" s="3">
         <v>-100</v>
       </c>
-      <c r="S102" s="3">
-        <v>0</v>
-      </c>
       <c r="T102" s="3">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="U102" s="3">
         <v>-100</v>
       </c>
       <c r="V102" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="W102" s="3">
         <v>0</v>
       </c>
       <c r="X102" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y102" s="3">
         <v>0</v>
       </c>
     </row>
